--- a/branches/dev/StructureDefinition-preview-model.xlsx
+++ b/branches/dev/StructureDefinition-preview-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T09:53:46+00:00</t>
+    <t>2026-08-27T20:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-preview-model.xlsx
+++ b/branches/dev/StructureDefinition-preview-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T20:51:52+00:00</t>
+    <t>2026-08-28T05:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-preview-model.xlsx
+++ b/branches/dev/StructureDefinition-preview-model.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.2</t>
+    <t>1.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T05:43:02+00:00</t>
+    <t>2026-08-28T09:59:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
